--- a/Unity/Assets/Config/Excel/Datas/StartConfig/RouterTest/StartZoneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/StartConfig/RouterTest/StartZoneConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\ET\Unity\Assets\Config\Excel\Datas\StartConfig\RouterTest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ChangeConfig\RouterTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F3B77A-9D46-482B-8B89-5FD55832DCC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43B46C8-D8FB-410A-9901-9AAD5D1C35D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>DBConnection</t>
   </si>
@@ -55,22 +55,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>数据库地址</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>mongodb://127.0.0.1</t>
-  </si>
-  <si>
-    <t>数据库地址</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库名</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>说明</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -83,10 +84,6 @@
   </si>
   <si>
     <t>路由区</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -94,7 +91,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,13 +120,6 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -172,11 +162,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -184,7 +171,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -510,63 +496,63 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="21" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="21" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:6" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="4"/>
+    </row>
+    <row r="2" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -574,32 +560,32 @@
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
         <v>3</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3" t="s">
         <v>16</v>
       </c>
     </row>
